--- a/rosters/2026-04.xlsx
+++ b/rosters/2026-04.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="65">
   <si>
     <t>Date</t>
   </si>
@@ -47,9 +47,6 @@
     <t>Wednesday</t>
   </si>
   <si>
-    <t>Sudhakar, Rubesh, Sujan</t>
-  </si>
-  <si>
     <t>Sharan</t>
   </si>
   <si>
@@ -203,13 +200,25 @@
     <t>Sudhakar, Maveera, Shiyam</t>
   </si>
   <si>
-    <t>Sharan, Sudhakar, Maveera, Shiyam</t>
-  </si>
-  <si>
     <t>Sudhakar, Maveera, Sujan, Shiyam</t>
   </si>
   <si>
     <t>Shree, Sujan, Shiyam, Rubesh</t>
+  </si>
+  <si>
+    <t>Rubesh, Sudhakar</t>
+  </si>
+  <si>
+    <t>Sharan, Amirdeshwara, Sudhakar</t>
+  </si>
+  <si>
+    <t>Sharan, Maveera, Shiyam</t>
+  </si>
+  <si>
+    <t>Shree, Sudhakar</t>
+  </si>
+  <si>
+    <t>Maveera, Shree, Shiyam, Sujan</t>
   </si>
 </sst>
 </file>
@@ -238,7 +247,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -251,8 +260,14 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -275,11 +290,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -296,6 +322,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -579,15 +607,15 @@
   <dimension ref="A1:Q31"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.21875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="4.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -618,16 +646,16 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -635,19 +663,19 @@
         <v>46114</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -655,31 +683,31 @@
         <v>46115</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N4" s="4" t="s">
+      <c r="O4" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="P4" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="Q4" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -687,25 +715,25 @@
         <v>46116</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="E5" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N5" s="5">
         <v>1</v>
       </c>
-      <c r="O5" s="3" t="s">
-        <v>28</v>
+      <c r="O5" s="8" t="s">
+        <v>27</v>
       </c>
       <c r="P5" s="3">
         <v>24</v>
@@ -719,25 +747,25 @@
         <v>46117</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="D6" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N6" s="5">
         <v>2</v>
       </c>
-      <c r="O6" s="3" t="s">
-        <v>15</v>
+      <c r="O6" s="8" t="s">
+        <v>14</v>
       </c>
       <c r="P6" s="3">
         <v>24</v>
@@ -751,25 +779,25 @@
         <v>46118</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="N7" s="5">
         <v>3</v>
       </c>
-      <c r="O7" s="3" t="s">
-        <v>21</v>
+      <c r="O7" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="P7" s="3">
         <v>24</v>
@@ -783,25 +811,25 @@
         <v>46119</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="D8" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N8" s="5">
         <v>4</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>8</v>
+      <c r="O8" s="8" t="s">
+        <v>7</v>
       </c>
       <c r="P8" s="3">
         <v>24</v>
@@ -818,20 +846,20 @@
         <v>6</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F9" s="3"/>
       <c r="N9" s="5">
         <v>5</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>25</v>
+      <c r="O9" s="8" t="s">
+        <v>24</v>
       </c>
       <c r="P9" s="3">
         <v>24</v>
@@ -845,25 +873,25 @@
         <v>46121</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N10" s="5">
         <v>6</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>17</v>
+      <c r="O10" s="8" t="s">
+        <v>16</v>
       </c>
       <c r="P10" s="3">
         <v>24</v>
@@ -877,25 +905,25 @@
         <v>46122</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N11" s="5">
         <v>7</v>
       </c>
-      <c r="O11" s="3" t="s">
-        <v>51</v>
+      <c r="O11" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="P11" s="3">
         <v>24</v>
@@ -909,25 +937,25 @@
         <v>46123</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="F12" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N12" s="6">
         <v>8</v>
       </c>
-      <c r="O12" s="7" t="s">
-        <v>9</v>
+      <c r="O12" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="P12" s="3">
         <v>24</v>
@@ -941,19 +969,19 @@
         <v>46124</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -961,19 +989,19 @@
         <v>46125</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -981,16 +1009,16 @@
         <v>46126</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F15" s="3"/>
     </row>
@@ -1002,52 +1030,55 @@
         <v>6</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F16" s="3"/>
+      <c r="G16" s="9"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
         <v>46128</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
         <v>46129</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1055,19 +1086,19 @@
         <v>46130</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1075,19 +1106,19 @@
         <v>46131</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1095,19 +1126,19 @@
         <v>46132</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1115,16 +1146,16 @@
         <v>46133</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F22" s="3"/>
     </row>
@@ -1136,13 +1167,13 @@
         <v>6</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F23" s="3"/>
     </row>
@@ -1151,37 +1182,39 @@
         <v>46135</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F24" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
         <v>46136</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1189,19 +1222,19 @@
         <v>46137</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1209,19 +1242,19 @@
         <v>46138</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>9</v>
-      </c>
       <c r="F27" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1229,19 +1262,19 @@
         <v>46139</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1249,16 +1282,16 @@
         <v>46140</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F29" s="3"/>
     </row>
@@ -1270,13 +1303,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F30" s="3"/>
     </row>
@@ -1285,16 +1318,16 @@
         <v>46142</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F31" s="3"/>
     </row>
